--- a/Tengine/Configs/GameConfig/Datas/Dialogue.xlsx
+++ b/Tengine/Configs/GameConfig/Datas/Dialogue.xlsx
@@ -108,16 +108,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -408,3253 +408,3253 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.95" customHeight="1" s="3">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>##comment</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>文案编号</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>阶段编号</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>句子顺序</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>说话者（源表为中文枚举词，未匹配 __enums__ 占位词表，按 string 读取）</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>说话者</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>对话正文</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>NPC职业编号</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30.95" customHeight="1" s="3">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>speaker</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>profession_id</t>
         </is>
       </c>
     </row>
     <row r="3" ht="50.1" customHeight="1" s="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>string#ref=ht.TbEvent</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>int#range=[1,]</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>int#range=[0,7]</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.95" customHeight="1" s="3">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" s="3">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>chat01_01_01</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>chat01_01</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>在大铁釜里撒盐得沉住气。味道淡了还能添，要是手抖倒多了，就得加麦酒和清水重新煮上半天。</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" s="3">
-      <c r="A6" s="9" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>chat02_01_01</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>chat02_01</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>整天忙着给冒险者烤肉炖汤，等轮到自己，炉火早熄了。啃口冷硬面包就着劣酒，倒也饿不死人。</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="3">
-      <c r="A7" s="9" t="inlineStr"/>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>chat03_01_01</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>chat03_01</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>客人砍价时总爱发誓说“下趟商队来还找你”。呵，在边境混久了就知道，这种承诺比地精的信誉还薄。</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" s="3">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>chat04_01_01</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>chat04_01</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>装货时总觉得驮兽背上塞满了必需品，可客人一张嘴，偏偏挑你货箱里没有的那样要。</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" s="3">
-      <c r="A9" s="9" t="inlineStr"/>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>chat05_01_01</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>chat05_01</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>在铁砧前敲了一整天，坐下来耳朵还在嗡嗡响。还是你这儿好，麦酒木杯碰在长桌上的声音，听着踏实。</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" s="3">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>chat06_01_01</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>chat06_01</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>总有毛头佣兵拿刚开刃的新剑去劈花岗岩。隔天抱着满刃豁口找回来，还一脸无辜地问我能不能修。</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" s="3">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>chat07_01_01</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>chat07_01</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>在井边搓了半天，指甲缝里还是黑土。我们这些侍弄麦田的，哪洗得干净手上的泥巴。</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" s="3">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>chat08_01_01</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>chat08_01</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>在田垄上还不觉得累，一跨进酒馆闻到麦香，两条腿顿时软了。……老板，借张木凳让我喘口气。</t>
         </is>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" s="3">
-      <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>chat09_01_01</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>chat09_01</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>这双厚牛皮战靴结实耐磨，就是踩在碎石路上咯吱响。在灌木丛里埋伏时，连我自己都嫌它吵。</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" s="3">
-      <c r="A14" s="9" t="inlineStr"/>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>chat10_01_01</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>chat10_01</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>看委托板我先看距离，再看银币。要是光赶路就耗光了体力，半路遇上魔物就是送死。</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" s="3">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>chat11_01_01</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>chat11_01</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>常有人嘴硬说只是犯困。可一探脉搏，眼圈熬得发黑……凡人的肉躯，哪经得起这么透支。</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" s="3">
-      <c r="A16" s="9" t="inlineStr"/>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>chat12_01_01</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>chat12_01</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>用圣水和绷带处理外伤不难，最难的是劝人休养。伤口刚结痂，他们就急着提剑去挣下一枚银币了。</t>
         </is>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" s="3">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>chat13_01_01</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>chat13_01</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>镇上那几首老调子客人比我还熟。我鲁特琴刚拨两个音，底下的醉汉就扯着破锣嗓子抢先唱完了。</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" s="3">
-      <c r="A18" s="9" t="inlineStr"/>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>chat14_01_01</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>chat14_01</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>我这脑袋记不住几张贵族的名字，但曲调忘不掉。只要哼两句当年的调子，对座那人的模样就浮出来了。</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" s="3">
-      <c r="A19" s="9" t="inlineStr"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>chat15_01_01</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>chat15_01</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>歇歇脚。</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" s="3">
-      <c r="A20" s="9" t="inlineStr"/>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>chat16_01_01</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>chat16_01</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>这酒不错。</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" s="3">
-      <c r="A21" s="9" t="inlineStr"/>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>chat17_01_01</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>chat17_01</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="D21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>再来一杯。</t>
         </is>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" s="3">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr"/>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>chat18_01_01</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>chat18_01</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>肚子有点饿了。</t>
         </is>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" s="3">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>chat19_01_01</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>chat19_01</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="D23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>坐会儿再走。</t>
         </is>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" s="3">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>chat20_01_01</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>chat20_01</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="D24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>今天不想赶路。</t>
         </is>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" s="3">
-      <c r="A25" s="9" t="inlineStr"/>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>chat21_01_01</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>chat21_01</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="D25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>难得清闲。</t>
         </is>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" s="3">
-      <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>chat22_01_01</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>chat22_01</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="D26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>客人</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>喝完这杯就走。</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" s="3">
-      <c r="A27" s="9" t="inlineStr"/>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>chat23_01_01</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>chat23_01</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="D27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>酒保</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>随便坐。</t>
         </is>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" s="3">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>chat24_01_01</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>chat24_01</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>酒保</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>慢慢喝。</t>
         </is>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" s="3">
-      <c r="A29" s="9" t="inlineStr"/>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>main01_01_01</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>main01_01</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="D29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>老板，近来荒原上的怪物闹得凶，路过的佣兵和斥候都在囤干粮。石炉里的炭火正旺，我本想烤上一大炉硬皮面包，可后厨的面粉袋全见底了，手边急缺一袋上好的小麦。</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" s="3">
-      <c r="A30" s="9" t="inlineStr"/>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>main01_01_02</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>main01_01</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>这年头要穿过魔物封锁运粮可不容易，你若是在镇上农夫手里弄到小麦，务必先替我留在柜台。</t>
         </is>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" s="3">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>main01_02_01</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>main01_02</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="D31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>小麦我已经替你备下了，颗粒饱满干燥。接下来这一炉面包，你打算怎么开工？</t>
         </is>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" s="3">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>main01_02_02</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>main01_02</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>酒馆里公事公办。你去悬赏栏立一份烹饪悬赏，写明用这批小麦烘烤面包。等契约和原料都定下来，我洗净双手就接单去磨粉揉面。</t>
         </is>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" s="3">
-      <c r="A33" s="9" t="inlineStr"/>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>main01_03_01</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>main01_03</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="D33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>老板，你在悬赏板上挂的那份面包委托，我已经全做完了，刚从石炉里铲出来！</t>
         </is>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" s="3">
-      <c r="A34" s="9" t="inlineStr"/>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr"/>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>main01_03_02</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>main01_03</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>焦黄酥脆的外皮裹着滚烫的麦香！在这刀口舔血的边境大陆，奔波整日的人啃上这么一口热干粮，才算真正活过来。</t>
         </is>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" s="3">
-      <c r="A35" s="9" t="inlineStr"/>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>main02_01_01</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>main02_01</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="D35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>老板，镇外黑松林的魔物爪牙越来越躁动，要在失落大陆上经营酒馆，不多备两件实用的防具可护不住周全。</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="n">
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>老板，近来路上的怪物越聚越多，要在失落大陆上经营酒馆，不多备两件实用的防具可护不住周全。</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" s="3">
-      <c r="A36" s="9" t="inlineStr"/>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>main02_01_02</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>main02_01</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>我车队刚从南境哨站拉来一批鞣制皮甲，既能防野兽爪牙又轻便透气。你瞧瞧成色，看这趟有没有合身的尺寸。</t>
         </is>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" s="3">
-      <c r="A37" s="9" t="inlineStr"/>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>main02_02_01</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>main02_02</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="D37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>爽快！皮甲穿在身上，好歹多了一层硬壳抵挡抓咬。不过荒野求生光挨打可不行，手里见血的真家伙备妥了吗？</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" s="3">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>main02_02_02</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>main02_02</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>要是行囊里还缺把趁手的铁剑，不妨挑挑我货箱里的存货，精铁开刃，劈开兽骨绝不含糊。</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" s="3">
-      <c r="A39" s="9" t="inlineStr"/>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr"/>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>main02_03_01</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>main02_03</t>
         </is>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="D39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>皮甲和铁剑都照顾了我的买卖，老板好眼力！我这趟冒着被魔物袭击的风险跑商总算没亏本，多谢关照。</t>
         </is>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" s="3">
-      <c r="A40" s="9" t="inlineStr"/>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>main02_03_02</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>main02_03</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>往后酒馆防卫要是还缺什么装备，尽管来我的货架翻。碰上断货也别急，等我下趟商队补给运到，保准给你留着。</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" s="3">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr"/>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>main03_01_01</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>main03_01</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="D41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>老板，市面上那些制式铁剑虽然粗重，但只要铁胚没暗裂，扔进风炉里多添硬木炭，还能重锻成吹毛断发的百炼长剑。</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1" s="3">
-      <c r="A42" s="9" t="inlineStr"/>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>main03_01_02</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>main03_01</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>凡铁要脱胎换骨可不是空谈，你得先在铺里备出一把规整的铁剑，咱们才能谈后续折叠锻打的重活。</t>
         </is>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1" s="3">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr"/>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>main03_02_01</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>main03_02</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="D43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>铁剑我已经备妥了，剑脊结实。如果要请你重新锻造，该走什么章程？</t>
         </is>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="G43" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1" s="3">
-      <c r="A44" s="9" t="inlineStr"/>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr"/>
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>main03_02_02</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>main03_02</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>按小镇规矩办事。去悬赏栏挂个锻造悬赏，羊皮纸上写明要重锻成百炼长剑。定金与材料齐备，我才能接单抡起重锤动工。</t>
         </is>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="G44" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1" s="3">
-      <c r="A45" s="9" t="inlineStr"/>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr"/>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>main03_03_01</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>main03_03</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="D45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>呼……你在悬赏板上留的锻造委托办结了，浸过淬火油的百炼长剑已经打好，沉甸甸的压手得很！</t>
         </is>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="G45" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" s="3">
-      <c r="A46" s="9" t="inlineStr"/>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>main03_03_02</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>main03_03</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>这回我可是使出了看家本领，反复折叠捶打出叠层纹路，剑刃淬火的硬度总算称了我的心意。拿去斩杀魔物，绝不崩刃！</t>
         </is>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1" s="3">
-      <c r="A47" s="9" t="inlineStr"/>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>main04_01_01</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>main04_01</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="D47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>老板，酒馆后厨迎来送往这么多佣兵和行商，做饭炖肉的麦料还够用吗？</t>
         </is>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1" s="3">
-      <c r="A48" s="9" t="inlineStr"/>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr"/>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>main04_01_02</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>main04_01</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="D48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>我的手推车上都是刚从田里打下的农产品。想收干燥饱满的小麦，就先来挑挑我这趟拉进镇的货。</t>
         </is>
       </c>
-      <c r="G48" s="9" t="n">
+      <c r="G48" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1" s="3">
-      <c r="A49" s="9" t="inlineStr"/>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr"/>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>main04_02_01</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>main04_02</t>
         </is>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="D49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>整袋小麦全清点给你了。不过说句实话，闻着麦穗这股清香，我肚里的馋虫全醒了，倒惦记起酒馆里刚出炉的面包。</t>
         </is>
       </c>
-      <c r="G49" s="9" t="n">
+      <c r="G49" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1" s="3">
-      <c r="A50" s="9" t="inlineStr"/>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr"/>
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>main04_02_02</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>main04_02</t>
         </is>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D50" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>我们这些在泥里刨食的，常年只吃糠皮麦糊。你柜台要是备有现成的白面烤面包，能不能匀我一个尝尝？</t>
         </is>
       </c>
-      <c r="G50" s="9" t="n">
+      <c r="G50" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1" s="3">
-      <c r="A51" s="9" t="inlineStr"/>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr"/>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>main04_03_01</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>main04_03</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="D51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>愿丰收保佑你！金黄松软的面包我收到了，热气直往脸上扑，多谢你的慷慨，老板。</t>
         </is>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1" s="3">
-      <c r="A52" s="9" t="inlineStr"/>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr"/>
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>main04_03_02</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>main04_03</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>我用粗亚麻布裹好塞进怀里，等下午在田里除草挥汗到脱力时，配着井水啃上一大口，力气就能全补回来了。</t>
         </is>
       </c>
-      <c r="G52" s="9" t="n">
+      <c r="G52" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1" s="3">
-      <c r="A53" s="9" t="inlineStr"/>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr"/>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>main05_01_01</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>main05_01</t>
         </is>
       </c>
-      <c r="D53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="D53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>老板，镇外的魔物最近活动猖獗，光靠粗木棒和匕首可抵挡不住利齿。我想挑一把结实顺手的铁剑，接战斗委托时好劈开一条生路。</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="n">
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>老板，镇外的怪物最近成群出现，光靠粗木棒和匕首可应付不来。我想挑一把结实顺手的铁剑，接战斗委托时好开出一条生路。</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1" s="3">
-      <c r="A54" s="9" t="inlineStr"/>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr"/>
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>main05_01_02</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>main05_01</t>
         </is>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="D54" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>我看酒馆库房里出入不少行商物资，你手头要是有多余的兵刃，能不能匀我一把？手里有了铁器，迈出镇门心里才踏实。</t>
         </is>
       </c>
-      <c r="G54" s="9" t="n">
+      <c r="G54" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1" s="3">
-      <c r="A55" s="9" t="inlineStr"/>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>main05_02_01</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>main05_02</t>
         </is>
       </c>
-      <c r="D55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="D55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>剑格稳当、重心恰到好处，这把铁剑我收下了，多谢老板关照！</t>
         </is>
       </c>
-      <c r="G55" s="9" t="n">
+      <c r="G55" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1" s="3">
-      <c r="A56" s="9" t="inlineStr"/>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr"/>
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>main05_02_02</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>main05_02</t>
         </is>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="D56" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>镇上要是有战斗悬赏就贴出来吧。我得先在板前摸清怪物的习性和巢穴地势，算清胜算，再决定接不接。</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="n">
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>镇上要是有战斗悬赏就贴出来吧。我得先在板前摸清那群怪物的数量和聚集地点，算清胜算，再决定接不接。</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" s="3">
-      <c r="A57" s="9" t="inlineStr"/>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr"/>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>main05_03_01</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>main05_03</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="D57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>呼……身上的血污总算擦干净了。那份讨伐悬赏我已经利落办完，手脚齐全，活着回来了！</t>
         </is>
       </c>
-      <c r="G57" s="9" t="n">
+      <c r="G57" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" s="3">
-      <c r="A58" s="9" t="inlineStr"/>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr"/>
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>main05_03_02</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>main05_03</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="D58" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>先容我拉张橡木椅坐下、灌碗凉麦酒。从荒原一路急行军赶回来，铁护胫磨得皮肉发烫，两条腿现在还在发抖。</t>
         </is>
       </c>
-      <c r="G58" s="9" t="n">
+      <c r="G58" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" s="3">
-      <c r="A59" s="9" t="inlineStr"/>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>main05_04_01</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>main05_04</t>
         </is>
       </c>
-      <c r="D59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="D59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>{事件角色名}在这次悬赏战斗中阵亡，悬赏未完成。</t>
         </is>
       </c>
-      <c r="G59" s="9" t="n">
+      <c r="G59" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1" s="3">
-      <c r="A60" s="9" t="inlineStr"/>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr"/>
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>main06_01_01</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>main06_01</t>
         </is>
       </c>
-      <c r="D60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="D60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>老板，你后厨里有刚烘烤好的面包吗？我想随身带上一个备用。</t>
         </is>
       </c>
-      <c r="G60" s="9" t="n">
+      <c r="G60" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1" s="3">
-      <c r="A61" s="9" t="inlineStr"/>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr"/>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>main06_01_02</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>main06_01</t>
         </is>
       </c>
-      <c r="D61" s="9" t="n">
+      <c r="D61" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>整日守在祈祷所为伤员净化创口，忙碌起来经常错过餐点，常常体力透支。手边有点现成充饥的干粮，施救时精神也更集中。</t>
         </is>
       </c>
-      <c r="G61" s="9" t="n">
+      <c r="G61" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" s="3">
-      <c r="A62" s="9" t="inlineStr"/>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr"/>
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>main06_02_01</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>main06_02</t>
         </is>
       </c>
-      <c r="D62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="D62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>松软的面包我收到了，愿神圣之光眷顾你的慷慨，谢谢你，老板。</t>
         </is>
       </c>
-      <c r="G62" s="9" t="n">
+      <c r="G62" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" s="3">
-      <c r="A63" s="9" t="inlineStr"/>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr"/>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>main06_02_02</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>main06_02</t>
         </is>
       </c>
-      <c r="D63" s="9" t="n">
+      <c r="D63" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>这样等会儿即便又有流血的冒险者被抬进来，我也能撑住体力，随时施展治疗祷言了。</t>
         </is>
       </c>
-      <c r="G63" s="9" t="n">
+      <c r="G63" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" s="3">
-      <c r="A64" s="9" t="inlineStr"/>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr"/>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>main06_03_01</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>main06_03</t>
         </is>
       </c>
-      <c r="D64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="D64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>我用药膏和治愈神术帮镇上的伤者处理了伤势，毒素清除了，断骨也已固定，大家的情况大有好转。</t>
         </is>
       </c>
-      <c r="G64" s="9" t="n">
+      <c r="G64" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" s="3">
-      <c r="A65" s="9" t="inlineStr"/>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr"/>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>main06_03_02</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>main06_03</t>
         </is>
       </c>
-      <c r="D65" s="9" t="n">
+      <c r="D65" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>照顾伤患是件漫长而耗费精力的差事，再怎么忙碌，自己也得按时吃些东西。若是医护者先倒下了，受苦的还是病人们。</t>
         </is>
       </c>
-      <c r="G65" s="9" t="n">
+      <c r="G65" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" s="3">
-      <c r="A66" s="9" t="inlineStr"/>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr"/>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>main07_01_01</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>main07_01</t>
         </is>
       </c>
-      <c r="D66" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="D66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>老板，失落大陆的荒原危机重重，想摸清镇外魔物的巡弋踪迹，找我这个常年在外游荡的眼线准没错。</t>
         </is>
       </c>
-      <c r="G66" s="9" t="n">
+      <c r="G66" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" s="3">
-      <c r="A67" s="9" t="inlineStr"/>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr"/>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>main07_01_02</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>main07_01</t>
         </is>
       </c>
-      <c r="D67" s="9" t="n">
+      <c r="D67" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>斥候和猎人在荒野上冒死探得的情报，有确凿消息我就能卖。银币价钱咱们当面核清，你再决定买不买。</t>
         </is>
       </c>
-      <c r="G67" s="9" t="n">
+      <c r="G67" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1" s="3">
-      <c r="A68" s="9" t="inlineStr"/>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>main07_02_01</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>main07_02</t>
         </is>
       </c>
-      <c r="D68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="D68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>这条情报说的是：{到来时间}，{地点}出现了{怪物名}。</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="n">
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>这条情报说的是：{到来时间}，{地点}出现了一群{怪物名}，共有{怪物数量}只。</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1" s="3">
-      <c r="A69" s="9" t="inlineStr"/>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr"/>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>main07_02_02</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>main07_02</t>
         </is>
       </c>
-      <c r="D69" s="9" t="n">
+      <c r="D69" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>若想在它袭击商道前除掉它，就去酒馆的悬赏板立一份悬赏，自会有贪求赏金的佣兵前去揭榜。</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="n">
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>若想在它们袭击商道前清除这群怪物，就去酒馆的悬赏板立一份悬赏，自会有贪求赏金的佣兵前去揭榜。</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" s="3">
-      <c r="A70" s="9" t="inlineStr"/>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr"/>
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>main07_03_01</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>main07_03</t>
         </is>
       </c>
-      <c r="D70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
+      <c r="D70" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>那只游荡怪物的讨伐悬赏，我已经正式发布在悬赏栏上了。</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="n">
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>那群怪物的讨伐悬赏，我已经正式发布在悬赏栏上了。</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1" s="3">
-      <c r="A71" s="9" t="inlineStr"/>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr"/>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>main07_03_02</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>main07_03</t>
         </is>
       </c>
-      <c r="D71" s="9" t="n">
+      <c r="D71" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>利落！荒原上的风吹草动我会继续留心，外头一有异常动向，我立刻回酒馆给你通风报信。</t>
         </is>
       </c>
-      <c r="G71" s="9" t="n">
+      <c r="G71" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1" s="3">
-      <c r="A72" s="9" t="inlineStr"/>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr"/>
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Ex01_01_01</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="D72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="D72" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>你买下的消息确凿无误。就在{到来时间}，黑松林边缘出现了一头游荡的野狼。</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="n">
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>你买下的消息确凿无误。就在{到来时间}，{地点}出现了一群{怪物名}，共有{怪物数量}只。</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1" s="3">
-      <c r="A73" s="9" t="inlineStr"/>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr"/>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>Ex01_01_02</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="D73" s="9" t="n">
+      <c r="D73" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>采药的和拉木料的都得走那条林道。绕远路得多耗两天，硬着头皮走又提心吊胆，这麻烦早晚得解决。</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="n">
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>采买和运货的人都得经过那一带。绕远路费工夫，硬着头皮走又提心吊胆，这麻烦早晚得解决。</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1" s="3">
-      <c r="A74" s="9" t="inlineStr"/>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr"/>
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>Ex01_01_03</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="D74" s="9" t="n">
+      <c r="D74" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E74" s="9" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>要是挂出悬赏，真有人敢接这趟差事吗？外头的林子有多凶险，大伙心里都有数。</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="n">
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>要是挂出悬赏，真有人敢接这趟差事吗？成群的怪物有多难对付，大伙心里都有数。</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1" s="3">
-      <c r="A75" s="9" t="inlineStr"/>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr"/>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Ex01_01_04</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="D75" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>悬赏栏只管标价，接不接是他们自己的盘算。有人图银币，有人缺口粮，但没人能向你担保一定平安。</t>
         </is>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="G75" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1" s="3">
-      <c r="A76" s="9" t="inlineStr"/>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr"/>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Ex01_01_05</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="D76" s="9" t="n">
+      <c r="D76" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>我明白了。既然林道卡着镇上的生计，这份悬赏单，我得找羊皮纸好好写写。</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="n">
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>我明白了。既然这群怪物挡着大伙的路，这份悬赏单，我得找羊皮纸好好写写。</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1" s="3">
-      <c r="A77" s="9" t="inlineStr"/>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr"/>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Ex01_02_01</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Ex01_02</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="D77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>悬赏已发布：清除黑松林的野狼。</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="n">
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>悬赏已发布：清除{地点}的这群{怪物名}。</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1" s="3">
-      <c r="A78" s="9" t="inlineStr"/>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr"/>
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Ex01_03_01</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Ex01_03</t>
         </is>
       </c>
-      <c r="D78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="D78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>悬赏已完成，目标野狼已被清除，报酬已结算。</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="n">
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>悬赏已完成，目标怪物已全部清除，报酬已结算。</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1" s="3">
-      <c r="A79" s="9" t="inlineStr"/>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr"/>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Ex01_04_01</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Ex01_04</t>
         </is>
       </c>
-      <c r="D79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="D79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>{接赏者名}在这次悬赏战斗中阵亡，悬赏未完成。</t>
         </is>
       </c>
-      <c r="G79" s="9" t="n">
+      <c r="G79" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1" s="3">
-      <c r="A80" s="9" t="inlineStr"/>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr"/>
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Ex01_05_01</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Ex01_05</t>
         </is>
       </c>
-      <c r="D80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="D80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>那头野狼已被其他人清除，无须再为它发布悬赏。</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="n">
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>这群怪物已被其他人全部清除，无须再为它们发布悬赏。</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1" s="3">
-      <c r="A81" s="9" t="inlineStr"/>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr"/>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>Ex01_06_01</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Ex01_06</t>
         </is>
       </c>
-      <c r="D81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="D81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>这份悬赏已终止。</t>
         </is>
       </c>
-      <c r="G81" s="9" t="n">
+      <c r="G81" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1" s="3">
-      <c r="A82" s="9" t="inlineStr"/>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr"/>
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Ex01_07_01</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Ex01_07</t>
         </is>
       </c>
-      <c r="D82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="D82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>黑松林那桩悬赏结了。那只狼已经处置掉，赏金也当面结清了。</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="n">
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>{地点}那桩悬赏结了。那群{怪物名}已经全部清除，赏金也结清了。</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1" s="3">
-      <c r="A83" s="9" t="inlineStr"/>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr"/>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Ex01_07_02</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Ex01_07</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n">
+      <c r="D83" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E83" s="9" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>呼……总算能松口气。虽说林子深处未必就太平，但起码运木料的脚夫今天敢走近道了。</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="n">
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>呼……总算能松口气。虽说以后未必一直太平，但起码今天经过那里的人能安心走路了。</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1" s="3">
-      <c r="A84" s="9" t="inlineStr"/>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr"/>
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Ex01_07_03</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Ex01_07</t>
         </is>
       </c>
-      <c r="D84" s="9" t="n">
+      <c r="D84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>路能走就好。只要车队能把货稳当运进镇，这笔银币就算没白花。</t>
         </is>
       </c>
-      <c r="G84" s="9" t="n">
+      <c r="G84" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1" s="3">
-      <c r="A85" s="9" t="inlineStr"/>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr"/>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Ex01_08_01</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Ex01_08</t>
         </is>
       </c>
-      <c r="D85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="D85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>去黑松林接赏的那位……没能活着回来。悬赏没办成，人折在林子里了。</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="n">
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>去{地点}接赏的那位……没能活着回来。悬赏没办成，人折在那里了。</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1" s="3">
-      <c r="A86" s="9" t="inlineStr"/>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Ex01_08_02</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Ex01_08</t>
         </is>
       </c>
-      <c r="D86" s="9" t="n">
+      <c r="D86" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="9" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>……是么。我只当那只狼会拖慢几趟脚程，没想到真搭进去一条命。买卖归买卖，这消息听着堵心。</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="n">
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>……是么。我只当那群怪物会拖慢几趟脚程，没想到真搭进去一条命。买卖归买卖，这消息听着堵心。</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1" s="3">
-      <c r="A87" s="9" t="inlineStr"/>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr"/>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Ex01_08_03</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Ex01_08</t>
         </is>
       </c>
-      <c r="D87" s="9" t="n">
+      <c r="D87" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E87" s="9" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>揭下悬赏前那是个名字，走出去后却是个活人。这木板上的分量，比我想的沉。</t>
         </is>
       </c>
-      <c r="G87" s="9" t="n">
+      <c r="G87" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1" s="3">
-      <c r="A88" s="9" t="inlineStr"/>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr"/>
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Ex02_01_01</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>Ex02_01</t>
         </is>
       </c>
-      <c r="D88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
+      <c r="D88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>别提{相关角色名}。以后只要那家伙坐在这张桌上，我就换个地方喝酒，省得反胃。</t>
         </is>
       </c>
-      <c r="G88" s="9" t="n">
+      <c r="G88" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1" s="3">
-      <c r="A89" s="9" t="inlineStr"/>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr"/>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Ex02_01_02</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Ex02_01</t>
         </is>
       </c>
-      <c r="D89" s="9" t="n">
+      <c r="D89" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E89" s="9" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>你们前阵子还能同桌碰杯，怎么突然闹成这样？要是出了什么误会，不妨直说。</t>
         </is>
       </c>
-      <c r="G89" s="9" t="n">
+      <c r="G89" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1" s="3">
-      <c r="A90" s="9" t="inlineStr"/>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr"/>
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>Ex02_01_03</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Ex02_01</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n">
+      <c r="D90" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="9" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>我头回撞见怪物吓得拔腿逃跑，私下当丑事告诉他。他倒好，转头就在酒桌上当笑话抖搂个干净！</t>
         </is>
       </c>
-      <c r="G90" s="9" t="n">
+      <c r="G90" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1" s="3">
-      <c r="A91" s="9" t="inlineStr"/>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr"/>
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Ex02_01_04</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>Ex02_01</t>
         </is>
       </c>
-      <c r="D91" s="9" t="n">
+      <c r="D91" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>把别人交心的话拿来寻开心，确实过分。我去问问他，听听他到底怎么想的。</t>
         </is>
       </c>
-      <c r="G91" s="9" t="n">
+      <c r="G91" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1" s="3">
-      <c r="A92" s="9" t="inlineStr"/>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr"/>
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Ex02_02_01</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>Ex02_02</t>
         </is>
       </c>
-      <c r="D92" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="D92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>{事件角色名}对你意见很大。他说自己当初信任你才交了底，你却转头在酒席上拿他逃跑的事取乐。</t>
         </is>
       </c>
-      <c r="G92" s="9" t="n">
+      <c r="G92" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1" s="3">
-      <c r="A93" s="9" t="inlineStr"/>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr"/>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>Ex02_02_02</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>Ex02_02</t>
         </is>
       </c>
-      <c r="D93" s="9" t="n">
+      <c r="D93" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="9" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>相关角色</t>
         </is>
       </c>
-      <c r="F93" s="9" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>就为这事？大家喝得正起劲，我就是顺嘴热个场子，又不是故意要编排他，至于记恨到现在吗？</t>
         </is>
       </c>
-      <c r="G93" s="9" t="n">
+      <c r="G93" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1" s="3">
-      <c r="A94" s="9" t="inlineStr"/>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr"/>
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Ex02_02_03</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>Ex02_02</t>
         </is>
       </c>
-      <c r="D94" s="9" t="n">
+      <c r="D94" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E94" s="9" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>他在意的不是那次出糗，而是掏心窝子告诉你的难堪，被你轻飘飘当成了下酒的佐料。</t>
         </is>
       </c>
-      <c r="G94" s="9" t="n">
+      <c r="G94" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1" s="3">
-      <c r="A95" s="9" t="inlineStr"/>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Ex02_02_04</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Ex02_02</t>
         </is>
       </c>
-      <c r="D95" s="9" t="n">
+      <c r="D95" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>相关角色</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>……我当时光顾着逗乐，真没琢磨这么多。嘴快惹了祸，我认。要是他肯听，我当面去跟他赔不是。</t>
         </is>
       </c>
-      <c r="G95" s="9" t="n">
+      <c r="G95" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96" ht="42" customHeight="1" s="3">
-      <c r="A96" s="9" t="inlineStr"/>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="A96" s="8" t="inlineStr"/>
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Ex02_03_01</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Ex02_03</t>
         </is>
       </c>
-      <c r="D96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="D96" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>我去找过{相关角色名}了。他说当时喝急了嘴上没把门，知道伤了你，想找机会当面赔罪。</t>
         </is>
       </c>
-      <c r="G96" s="9" t="n">
+      <c r="G96" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97" ht="42" customHeight="1" s="3">
-      <c r="A97" s="9" t="inlineStr"/>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr"/>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Ex02_03_02</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>Ex02_03</t>
         </is>
       </c>
-      <c r="D97" s="9" t="n">
+      <c r="D97" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E97" s="9" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>喝急了？一句“没恶意”就能把人当猴耍了？他要是真顾及我的脸面，当初酒杯一端就不会胡吣！</t>
         </is>
       </c>
-      <c r="G97" s="9" t="n">
+      <c r="G97" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1" s="3">
-      <c r="A98" s="9" t="inlineStr"/>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr"/>
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Ex02_03_03</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>Ex02_03</t>
         </is>
       </c>
-      <c r="D98" s="9" t="n">
+      <c r="D98" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>原不原谅由你自己拿捏，我不会劝你大度。话我带到了，听不听他的解释，你自己拿主意。</t>
         </is>
       </c>
-      <c r="G98" s="9" t="n">
+      <c r="G98" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1" s="3">
-      <c r="A99" s="9" t="inlineStr"/>
-      <c r="B99" s="9" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr"/>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Ex02_03_04</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>Ex02_03</t>
         </is>
       </c>
-      <c r="D99" s="9" t="n">
+      <c r="D99" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>呼……行吧。既然他没躲着，改天他要是敢来，我就听听他嘴里能吐出什么话来。</t>
         </is>
       </c>
-      <c r="G99" s="9" t="n">
+      <c r="G99" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1" s="3">
-      <c r="A100" s="9" t="inlineStr"/>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr"/>
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>favor01_01_01</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>favor01_01</t>
         </is>
       </c>
-      <c r="D100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="D100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>小时候刚学侍弄麦田，我总把黑麦草和初生的麦苗认混，伸手就要拔。我父亲一巴掌拍开我的手，也不动怒，就拉我蹲在覆着白霜的泥垄旁，用粗糙的手指一株株掐开茎叶指给我看。</t>
         </is>
       </c>
-      <c r="G100" s="9" t="n">
+      <c r="G100" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" s="3">
-      <c r="A101" s="9" t="inlineStr"/>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr"/>
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>favor01_01_02</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>favor01_01</t>
         </is>
       </c>
-      <c r="D101" s="9" t="n">
+      <c r="D101" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>那时只嫌他念叨个没完。直到后来遇上凛冬饥荒，自己顶门立户侍弄田地，眼看冻裂的麦穗，拔错一株都心如刀割，我才明白他当年教我的不是认草，是在失落大陆的严冬里活下去的本事。</t>
         </is>
       </c>
-      <c r="G101" s="9" t="n">
+      <c r="G101" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="102" ht="42" customHeight="1" s="3">
-      <c r="A102" s="9" t="inlineStr"/>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="A102" s="8" t="inlineStr"/>
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>favor01_02_01</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>favor01_02</t>
         </is>
       </c>
-      <c r="D102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="D102" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>每年只要秋收磨下第一批新面粉，哪怕赋税再重，我母亲也总要起个大早烤麦饼。整间石屋飘满焦香，吃到最后，全家连粗木盘里掉下的干硬碎屑都舍不得浪费半点。</t>
         </is>
       </c>
-      <c r="G102" s="9" t="n">
+      <c r="G102" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="103" ht="42" customHeight="1" s="3">
-      <c r="A103" s="9" t="inlineStr"/>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr"/>
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>favor01_02_02</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>favor01_02</t>
         </is>
       </c>
-      <c r="D103" s="9" t="n">
+      <c r="D103" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>我也曾眼馋想学揉面，可农汉手劲不知轻重，面团总被我揉得像块生石胚。她掰开尝了一口直笑，打趣说我把在地里跟冻土较劲的蛮力，全使在面盆上了。</t>
         </is>
       </c>
-      <c r="G103" s="9" t="n">
+      <c r="G103" s="8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="104" ht="42" customHeight="1" s="3">
-      <c r="A104" s="9" t="inlineStr"/>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>favor02_01_01</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>favor02_01</t>
         </is>
       </c>
-      <c r="D104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="D104" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>刚进铺子给老铁匠当学徒那几年，他连剑胚都不许我摸，只逼着我对着砧子敲铁钉。他说连根钉子都打不直溜的学徒，要是敢碰兵刃，送去战场就是在谋杀佣兵的性命。</t>
         </is>
       </c>
-      <c r="G104" s="9" t="n">
+      <c r="G104" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1" s="3">
-      <c r="A105" s="9" t="inlineStr"/>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr"/>
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>favor02_01_02</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>favor02_01</t>
         </is>
       </c>
-      <c r="D105" s="9" t="n">
+      <c r="D105" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>我年轻气盛不服管，偷偷拿自己敲的钉子去钉铺里的长条木凳。结果一屁股坐上去当场散了架，满地都是砸弯的废钉，被老头子好一顿数落。</t>
         </is>
       </c>
-      <c r="G105" s="9" t="n">
+      <c r="G105" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="106" ht="42" customHeight="1" s="3">
-      <c r="A106" s="9" t="inlineStr"/>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr"/>
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>favor02_02_01</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>favor02_02</t>
         </is>
       </c>
-      <c r="D106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="D106" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
         <is>
           <t>后来我终于亲手锻出了第一把真正的钢剑。那是我的心血，根本舍不得卖，特意擦得雪亮端正地架在铺子正中央，老头子天天拿扫帚轰我收起来，我都赖着不肯挪。</t>
         </is>
       </c>
-      <c r="G106" s="9" t="n">
+      <c r="G106" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="107" ht="42" customHeight="1" s="3">
-      <c r="A107" s="9" t="inlineStr"/>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr"/>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>favor02_02_02</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>favor02_02</t>
         </is>
       </c>
-      <c r="D107" s="9" t="n">
+      <c r="D107" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E107" s="9" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>真被过路骑士买走那天，我心里空落落的，一路追到小镇栅栏门前，抓着人家的马缰叮嘱千万别拿它劈顽石。那骑手早跑得没影了，我还攥着满手铁灰，在冷风里呆呆站了半晌。</t>
         </is>
       </c>
-      <c r="G107" s="9" t="n">
+      <c r="G107" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="108" ht="42" customHeight="1" s="3">
-      <c r="A108" s="9" t="inlineStr"/>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr"/>
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>favor03_01_01</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>favor03_01</t>
         </is>
       </c>
-      <c r="D108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="D108" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F108" s="9" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>我刚学弹琴在荒原游荡那年，在泥沼哨站旁遇过一个胸甲破碎、咯着血沫的老雇佣兵。他嫌我唱的宫廷情歌太虚伪，拼着最后一口气，非逼着我学一段荒原斥候的旧调。</t>
         </is>
       </c>
-      <c r="G108" s="9" t="n">
+      <c r="G108" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="109" ht="42" customHeight="1" s="3">
-      <c r="A109" s="9" t="inlineStr"/>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr"/>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>favor03_01_02</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>favor03_01</t>
         </is>
       </c>
-      <c r="D109" s="9" t="n">
+      <c r="D109" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>他说“快死的人不想听什么骑士加冕，只想听暴风雪夜里老家壁炉的柴火响”。后来他没熬过那场寒夜，这把边角磨损的老鲁特琴，就是他咽气前留给我的。</t>
         </is>
       </c>
-      <c r="G109" s="9" t="n">
+      <c r="G109" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="110" ht="42" customHeight="1" s="3">
-      <c r="A110" s="9" t="inlineStr"/>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr"/>
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>favor03_02_01</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>favor03_02</t>
         </is>
       </c>
-      <c r="D110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="D110" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>后来我第一次在真正的边境酒馆登台，台下坐满刀疤脸的亡命徒。我吓得指节僵硬弹错了第一个泛音，整间石屋瞬间鸦雀无声，甚至能听见短剑出鞘的微响。</t>
         </is>
       </c>
-      <c r="G110" s="9" t="n">
+      <c r="G110" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1" s="3">
-      <c r="A111" s="9" t="inlineStr"/>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr"/>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>favor03_02_02</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>favor03_02</t>
         </is>
       </c>
-      <c r="D111" s="9" t="n">
+      <c r="D111" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>事件角色</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>我硬着头皮闭上眼，扯开嗓子唱起了那段老调。等唱完睁开眼，没人拔剑，昏暗的牛油火把下，几个满脸风霜的汉子默默低着头，正往木酒杯里倒烈酒。</t>
         </is>
       </c>
-      <c r="G111" s="9" t="n">
+      <c r="G111" s="8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3687,3782 +3687,3782 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.95" customHeight="1" s="3">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>##comment</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>阶段编号</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>事件编号</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>事件名称 备注</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>文案类别（源表为中文枚举词，未匹配 __enums__ 占位词表，按 string 读取）</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>职业（源值含“不限”，ht.Profession 无该别名，按 string 读取，不修改共享枚举）</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>文案类别</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>职业</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>前置阶段</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
-        <is>
-          <t>出现条件（源表为中文枚举词，未匹配 __enums__ 占位词表，按 string 读取）</t>
-        </is>
-      </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>出现条件</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>关联物品编号</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>关联怪物编号</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>需求数量</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>好感度门槛</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>抽取权重</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>推进说明 备注</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30.95" customHeight="1" s="3">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>#title</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>profession</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>previous_id</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>trigger</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>monster_id</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>required_count</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>favor_threshold</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>#note</t>
         </is>
       </c>
     </row>
     <row r="3" ht="50.1" customHeight="1" s="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr"/>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>string#ref=ht.TbEvent?</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>int#range=[0,]</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>int#range=[0,]</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>int#range=[0,]</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>int#range=[0,]</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>int#range=[0,]</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="30.95" customHeight="1" s="3">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1" s="3">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>chat01_01</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>chat01</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>厨师闲聊1</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" s="3">
-      <c r="A6" s="9" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>chat02_01</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>chat02</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>厨师闲聊2</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="3">
-      <c r="A7" s="9" t="inlineStr"/>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>chat03_01</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>chat03</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>商人闲聊1</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>商人</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
+      <c r="I7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" s="3">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>chat04_01</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>chat04</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>商人闲聊2</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>商人</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="I8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" s="3">
-      <c r="A9" s="9" t="inlineStr"/>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>chat05_01</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>chat05</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>铁匠闲聊1</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11" t="n">
+      <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" s="3">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>chat06_01</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>chat06</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>铁匠闲聊2</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11" t="n">
+      <c r="I10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" s="3">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>chat07_01</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>chat07</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>农民闲聊1</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="n">
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" s="3">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>chat08_01</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>chat08</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>农民闲聊2</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="11" t="n">
+      <c r="I12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" s="3">
-      <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>chat09_01</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>chat09</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>战士闲聊1</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="11" t="n">
+      <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" s="3">
-      <c r="A14" s="9" t="inlineStr"/>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>chat10_01</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>chat10</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>战士闲聊2</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="11" t="n">
+      <c r="I14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" s="3">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>chat11_01</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>chat11</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>牧师闲聊1</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>牧师</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11" t="n">
+      <c r="I15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" s="3">
-      <c r="A16" s="9" t="inlineStr"/>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>chat12_01</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>chat12</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>牧师闲聊2</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>牧师</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11" t="n">
+      <c r="I16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" s="3">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>chat13_01</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>chat13</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>吟游诗人闲聊1</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="11" t="n">
+      <c r="I17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" s="3">
-      <c r="A18" s="9" t="inlineStr"/>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>chat14_01</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>chat14</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>吟游诗人闲聊2</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="11" t="n">
+      <c r="I18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>无其他可播事件时，从当前职业闲聊中按抽取权重选一段；同一NPC当天沿用结果，次日优先换另一段。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" s="3">
-      <c r="A19" s="9" t="inlineStr"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>chat15_01</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>chat15</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊1</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="11" t="n">
+      <c r="I19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" s="3">
-      <c r="A20" s="9" t="inlineStr"/>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>chat16_01</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>chat16</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊2</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="11" t="n">
+      <c r="I20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" s="3">
-      <c r="A21" s="9" t="inlineStr"/>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>chat17_01</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>chat17</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊3</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11" t="n">
+      <c r="I21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" s="3">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr"/>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>chat18_01</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>chat18</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊4</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="11" t="n">
+      <c r="I22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" s="3">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>chat19_01</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>chat19</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊5</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="11" t="n">
+      <c r="I23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" s="3">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>chat20_01</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>chat20</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊6</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="11" t="n">
+      <c r="I24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N24" s="11" t="inlineStr">
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" s="3">
-      <c r="A25" s="9" t="inlineStr"/>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>chat21_01</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>chat21</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊7</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="11" t="n">
+      <c r="I25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" s="3">
-      <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>chat22_01</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>chat22</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>无职业客人闲聊8</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="11" t="n">
+      <c r="I26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N26" s="11" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为客人的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" s="3">
-      <c r="A27" s="9" t="inlineStr"/>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>chat23_01</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>chat23</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>酒保闲聊1</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="11" t="n">
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为酒保的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" s="3">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>chat24_01</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>chat24</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>酒保闲聊2</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>普通闲聊</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>日常交谈</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="11" t="n">
+      <c r="I28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N28" s="11" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>仅无职业且身份为酒保的NPC在酒馆交谈时可选；职业编号0，按说话者身份筛选。无其他可播事件时，在同身份条目中按抽取权重选取（默认1000）；同一NPC当天沿用结果，次日优先换另一条。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" s="3">
-      <c r="A29" s="9" t="inlineStr"/>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>main01_01</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>main01</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>烤一炉面包</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="11" t="n">
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N29" s="11" t="inlineStr">
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时绑定当前厨师；交谈不接取悬赏，也不扣原料。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" s="3">
-      <c r="A30" s="9" t="inlineStr"/>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>main01_02</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>main01</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>烤一炉面包</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>main01_01</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>持有物品时交谈</t>
         </is>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="11" t="n">
+      <c r="J30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N30" s="11" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>前段已读，玩家当前背包持有至少1份小麦，与绑定厨师交谈；库存可用，此门槛不代表已备齐悬赏用料。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" s="3">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>main01_03</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>main01</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>烤一炉面包</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>main01_02</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>本人烹饪完成后交谈</t>
         </is>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="11" t="n">
+      <c r="J31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>前段读完后发布烹饪悬赏，由绑定厨师自主接取并完成；同一悬赏实际结算面包至少1个后交谈。每天一次、原料校验沿用职业规则。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" s="3">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>main02_01</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>main02</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>买点实用的</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>商人</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="11" t="n">
+      <c r="I32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N32" s="11" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时绑定当前商人；可售商品以其实际库存和交易条件为准。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" s="3">
-      <c r="A33" s="9" t="inlineStr"/>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>main02_02</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>main02</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>买点实用的</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>商人</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>main02_01</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>向本人购买后交谈</t>
         </is>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="11" t="n">
+      <c r="J33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>前段读完后，向绑定商人成功买入皮甲累计至少1件，再交谈；赠与、索取、其他商人交易不计。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" s="3">
-      <c r="A34" s="9" t="inlineStr"/>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr"/>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>main02_03</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>main02</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>买点实用的</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>商人</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>main02_02</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>向本人购买后交谈</t>
         </is>
       </c>
-      <c r="I34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="11" t="n">
+      <c r="I34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>前段读完后，向绑定商人成功买入铁剑累计至少1把，再交谈；赠与、索取、其他商人交易不计。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" s="3">
-      <c r="A35" s="9" t="inlineStr"/>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>main03_01</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>main03</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>铁剑还能再锻</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="11" t="n">
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N35" s="11" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时绑定当前铁匠；交谈不接取悬赏，也不扣材料。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" s="3">
-      <c r="A36" s="9" t="inlineStr"/>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>main03_02</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>main03</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>铁剑还能再锻</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>main03_01</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>持有物品时交谈</t>
         </is>
       </c>
-      <c r="I36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="11" t="n">
+      <c r="I36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N36" s="11" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>前段已读，玩家当前背包持有至少1把铁剑，与绑定铁匠交谈；库存可用，此门槛不代表已备齐悬赏用料。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" s="3">
-      <c r="A37" s="9" t="inlineStr"/>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>main03_03</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>main03</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>铁剑还能再锻</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>main03_02</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>本人锻造完成后交谈</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="11" t="n">
+      <c r="J37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N37" s="11" t="inlineStr">
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>前段读完后发布锻造悬赏，由绑定铁匠自主接取并完成；同一悬赏实际结算百炼长剑至少1把后交谈。每天一次、材料校验沿用职业规则。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" s="3">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>main04_01</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>main04</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>小麦做的面包</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="11" t="n">
+      <c r="I38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时绑定当前农民；可售农产品以其实际库存和交易条件为准。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" s="3">
-      <c r="A39" s="9" t="inlineStr"/>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr"/>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>main04_02</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>main04</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>小麦做的面包</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>main04_01</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>向本人购买后交谈</t>
         </is>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="I39" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="11" t="n">
+      <c r="J39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="N39" s="9" t="inlineStr">
         <is>
           <t>前段读完后，向绑定农民成功买入小麦累计至少1份，再交谈；赠与、索取、其他农民交易不计。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" s="3">
-      <c r="A40" s="9" t="inlineStr"/>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>main04_03</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>main04</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>小麦做的面包</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>main04_02</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>交付物品后交谈</t>
         </is>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="11" t="n">
+      <c r="J40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N40" s="11" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>前段读完后，通过交易确认向绑定农民赠与或卖出面包，实际转入其背包累计至少1个，再交谈；不要求已食用。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" s="3">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr"/>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>main05_01</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>main05</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>出门前备好剑</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="11" t="n">
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N41" s="11" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时绑定当前战士；交谈不指定其接取悬赏。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1" s="3">
-      <c r="A42" s="9" t="inlineStr"/>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>main05_02</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>main05</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>出门前备好剑</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>main05_01</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>交付物品后交谈</t>
         </is>
       </c>
-      <c r="I42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="11" t="n">
+      <c r="I42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N42" s="11" t="inlineStr">
+      <c r="N42" s="9" t="inlineStr">
         <is>
           <t>前段读完后，通过交易确认向绑定战士赠与或卖出铁剑，实际转入其背包累计至少1把，再交谈；不要求已装备。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1" s="3">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr"/>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>main05_03</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>main05</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>出门前备好剑</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>main05_02</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>本人战斗完成并返馆</t>
         </is>
       </c>
-      <c r="I43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="11" t="n">
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N43" s="11" t="inlineStr">
+      <c r="N43" s="9" t="inlineStr">
         <is>
           <t>前段读完后发布战斗悬赏，由绑定战士自主接取、完成并结算；本人存活返馆后交谈。其他角色完成不计。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1" s="3">
-      <c r="A44" s="9" t="inlineStr"/>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr"/>
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>main05_04</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>main05</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>出门前备好剑</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>main05_02</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>本人悬赏战斗死亡</t>
         </is>
       </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="11" t="n">
+      <c r="I44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N44" s="11" t="inlineStr">
+      <c r="N44" s="9" t="inlineStr">
         <is>
           <t>绑定战士在本次已绑定悬赏的战斗中阵亡，且该悬赏未完成时显示系统提示；与成功返馆互斥，读完结束主线。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1" s="3">
-      <c r="A45" s="9" t="inlineStr"/>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr"/>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>main06_01</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>main06</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>先备些吃的</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>牧师</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="11" t="n">
+      <c r="I45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N45" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时绑定当前牧师；索要面包是剧情请求，不是治疗技能的消耗或使用条件。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" s="3">
-      <c r="A46" s="9" t="inlineStr"/>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>main06_02</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>main06</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>先备些吃的</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>牧师</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>main06_01</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>交付物品后交谈</t>
         </is>
       </c>
-      <c r="I46" s="9" t="n">
+      <c r="I46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="11" t="n">
+      <c r="J46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N46" s="11" t="inlineStr">
+      <c r="N46" s="9" t="inlineStr">
         <is>
           <t>前段读完后，通过交易确认向绑定牧师赠与或卖出面包，实际转入其背包累计至少1个，再交谈；不要求已食用。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1" s="3">
-      <c r="A47" s="9" t="inlineStr"/>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>main06_03</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>main06</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>先备些吃的</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>牧师</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>main06_02</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>本人治疗完成后交谈</t>
         </is>
       </c>
-      <c r="I47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="11" t="n">
+      <c r="I47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N47" s="11" t="inlineStr">
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>前段读完后，绑定牧师实际为一名存活且受伤的城镇NPC恢复生命，再交谈；自然恢复、食用物品和无实际回血的治疗不计。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1" s="3">
-      <c r="A48" s="9" t="inlineStr"/>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr"/>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>main07_01</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>main07</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>把消息问清楚</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>首次交谈</t>
         </is>
       </c>
-      <c r="I48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="11" t="n">
+      <c r="I48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N48" s="11" t="inlineStr">
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>首次播放本主线时只绑定当前吟游诗人；介绍情报购买，不直接赠送怪物情报。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1" s="3">
-      <c r="A49" s="9" t="inlineStr"/>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr"/>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>main07_02</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>main07</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>把消息问清楚</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>main07_01</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>购得新怪物情报</t>
         </is>
       </c>
-      <c r="I49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="11" t="n">
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N49" s="11" t="inlineStr">
-        <is>
-          <t>前段读完后有新怪物到来，玩家向绑定诗人成功购买该次情报后播放；购买时目标存活且无玩家针对它的悬赏。未成交不播详情。</t>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t>前段读完后有新怪物组到来，玩家向绑定诗人成功购买该组情报后播放；购买时组内至少一只存活且无玩家针对该组的悬赏。未成交不播详情。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1" s="3">
-      <c r="A50" s="9" t="inlineStr"/>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr"/>
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>main07_03</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>main07</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>把消息问清楚</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>主线事件</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>main07_02</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>关联悬赏发布后交谈</t>
         </is>
       </c>
-      <c r="I50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="11" t="n">
+      <c r="I50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N50" s="11" t="inlineStr">
-        <is>
-          <t>针对上一段绑定的怪物实例发布悬赏成功后，与绑定诗人交谈；读取实际发布记录，不由本段代发悬赏。</t>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t>针对上一段绑定的怪物组实例发布悬赏成功后，与绑定诗人交谈；读取实际发布记录，不由本段代发悬赏。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1" s="3">
-      <c r="A51" s="9" t="inlineStr"/>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr"/>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>购得新怪物情报</t>
         </is>
       </c>
-      <c r="I51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="11" t="n">
+      <c r="I51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N51" s="11" t="inlineStr">
-        <is>
-          <t>野狼在黑松林实际到来，玩家向知情诗人成功购买该次情报后播放；购买时目标存活且无对应悬赏。与main07_02命中同次购买时只播本段并同步进度。</t>
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>任一种已解锁怪物组在随机场地实际生成，玩家向知情诗人成功购买该组情报后播放；monster_id=0，不限制怪种与场地。购买时组内至少一只存活且无对应悬赏。与main07_02命中同次购买时只播本段并同步进度。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1" s="3">
-      <c r="A52" s="9" t="inlineStr"/>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr"/>
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Ex01_02</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>关联悬赏发布</t>
         </is>
       </c>
-      <c r="I52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="11" t="n">
+      <c r="I52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N52" s="11" t="inlineStr">
-        <is>
-          <t>本次绑定野狼的悬赏发布成功后显示系统提示；前段未读完时保留记录，待其读完再播。</t>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t>本次绑定怪物组的悬赏发布成功后显示系统提示；目标数量取发布时存活成员数。前段未读完时保留记录，待其读完再播。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1" s="3">
-      <c r="A53" s="9" t="inlineStr"/>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr"/>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Ex01_03</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Ex01_02</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>关联悬赏完成</t>
         </is>
       </c>
-      <c r="I53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="11" t="n">
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N53" s="11" t="inlineStr">
+      <c r="N53" s="9" t="inlineStr">
         <is>
           <t>同一悬赏成功且报酬已结算后播放；与阵亡、其他终止分支互斥。读完等待Ex01_07，诗人死亡或永久离开则直接结束。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1" s="3">
-      <c r="A54" s="9" t="inlineStr"/>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr"/>
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Ex01_04</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Ex01_02</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>关联悬赏战斗死亡</t>
         </is>
       </c>
-      <c r="I54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="11" t="n">
+      <c r="I54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N54" s="11" t="inlineStr">
+      <c r="N54" s="9" t="inlineStr">
         <is>
           <t>实际接赏者在同一悬赏战斗中阵亡且悬赏失败后播放；与成功、其他终止分支互斥。读完等待Ex01_08，诗人死亡或永久离开则直接结束。</t>
         </is>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1" s="3">
-      <c r="A55" s="9" t="inlineStr"/>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Ex01_05</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Ex01_01</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>目标提前清除</t>
         </is>
       </c>
-      <c r="I55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="11" t="n">
+      <c r="I55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N55" s="11" t="inlineStr">
-        <is>
-          <t>购买情报后、玩家发布悬赏前，同一野狼被其他人清除；前段读完后显示，不再进入发布分支。</t>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t>购买情报后、玩家发布悬赏前，同一怪物组的全部成员已被其他人清除；前段读完后显示，不再进入发布分支。</t>
         </is>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1" s="3">
-      <c r="A56" s="9" t="inlineStr"/>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr"/>
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Ex01_06</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Ex01_02</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>关联悬赏终止</t>
         </is>
       </c>
-      <c r="I56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="11" t="n">
+      <c r="I56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N56" s="11" t="inlineStr">
+      <c r="N56" s="9" t="inlineStr">
         <is>
           <t>同一悬赏因接赏者阵亡以外的原因失败、失效或取消后播放；与成功、阵亡分支互斥，读完结束本次事件。</t>
         </is>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" s="3">
-      <c r="A57" s="9" t="inlineStr"/>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr"/>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Ex01_07</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Ex01_03</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>关联悬赏完成后交谈</t>
         </is>
       </c>
-      <c r="I57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="11" t="n">
+      <c r="I57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N57" s="11" t="inlineStr">
-        <is>
-          <t>Ex01_03已读后，与原出售情报的诗人交谈；沿用同一野狼和悬赏的成功、结算记录。诗人暂离则等待，死亡或永久离开则结束；本段读完结束成功分支。</t>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>Ex01_03已读后，与原出售情报的诗人交谈；沿用同一怪物组实例和悬赏的成功、结算记录。诗人暂离则等待，死亡或永久离开则结束；本段读完结束成功分支。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" s="3">
-      <c r="A58" s="9" t="inlineStr"/>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr"/>
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Ex01_08</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Ex01</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>黑松林的狼</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>路上的怪物群</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Ex01_04</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>关联悬赏阵亡后交谈</t>
         </is>
       </c>
-      <c r="I58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="11" t="n">
+      <c r="I58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N58" s="11" t="inlineStr">
+      <c r="N58" s="9" t="inlineStr">
         <is>
           <t>Ex01_04已读后，与原出售情报的诗人交谈；沿用同一悬赏的接赏者战斗阵亡及失败记录。诗人暂离则等待，死亡或永久离开则结束；本段读完结束阵亡分支。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" s="3">
-      <c r="A59" s="9" t="inlineStr"/>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Ex02_01</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>Ex02</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>不该说的笑话</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>NPC关系转为敌对</t>
         </is>
       </c>
-      <c r="I59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="11" t="n">
+      <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N59" s="11" t="inlineStr">
+      <c r="N59" s="9" t="inlineStr">
         <is>
           <t>A对B的好感由非负降至负数后，与A交谈并绑定双方及本次变化；初始负好感不触发。本事件采用B把A私下告知的逃跑经历当作酒桌笑话的背景；已记录其他冲突缘由时不选本事件。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1" s="3">
-      <c r="A60" s="9" t="inlineStr"/>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr"/>
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Ex02_02</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Ex02</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>不该说的笑话</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Ex02_01</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>与关系另一方交谈</t>
         </is>
       </c>
-      <c r="I60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="11" t="n">
+      <c r="I60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N60" s="11" t="inlineStr">
+      <c r="N60" s="9" t="inlineStr">
         <is>
           <t>前段已读后与绑定的B交谈；A、B均存活且A对B的好感仍为负数。B承认嘴快伤人并愿意当面道歉，尚未实际道歉或与A和好。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1" s="3">
-      <c r="A61" s="9" t="inlineStr"/>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr"/>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Ex02_03</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Ex02</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>不该说的笑话</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Ex02_02</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>返回事件角色交谈</t>
         </is>
       </c>
-      <c r="I61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="11" t="n">
+      <c r="I61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N61" s="11" t="inlineStr">
+      <c r="N61" s="9" t="inlineStr">
         <is>
           <t>前段已读后返回绑定的A交谈；A、B均存活且A对B的好感仍为负数。A愿意听解释，尚未原谅或和好；读完结束，不自动改变双方好感。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" s="3">
-      <c r="A62" s="9" t="inlineStr"/>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr"/>
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>favor01_01</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>favor01</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>小时候的麦田</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>好感度对话</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>好感达到门槛</t>
         </is>
       </c>
-      <c r="I62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="11" t="n">
+      <c r="I62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="M62" s="11" t="n">
+      <c r="M62" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N62" s="11" t="inlineStr">
+      <c r="N62" s="9" t="inlineStr">
         <is>
           <t>NPC对玩家的当前好感至少5；首框显示时绑定本人，读完不重复。其他同职业NPC不共用这段往事。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" s="3">
-      <c r="A63" s="9" t="inlineStr"/>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr"/>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>favor01_02</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>favor01</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>小时候的麦田</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>好感度对话</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>农民</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>favor01_01</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>好感达到门槛</t>
         </is>
       </c>
-      <c r="I63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="11" t="n">
+      <c r="I63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M63" s="11" t="n">
+      <c r="M63" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N63" s="11" t="inlineStr">
+      <c r="N63" s="9" t="inlineStr">
         <is>
           <t>前段已读，与绑定NPC交谈且当前好感至少10时播放；开播前复核，读完不重复。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" s="3">
-      <c r="A64" s="9" t="inlineStr"/>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr"/>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>favor02_01</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>favor02</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>刚学打铁那会儿</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>好感度对话</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>好感达到门槛</t>
         </is>
       </c>
-      <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="11" t="n">
+      <c r="I64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="M64" s="11" t="n">
+      <c r="M64" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N64" s="11" t="inlineStr">
+      <c r="N64" s="9" t="inlineStr">
         <is>
           <t>NPC对玩家的当前好感至少5；首框显示时绑定本人，读完不重复。其他同职业NPC不共用这段往事。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" s="3">
-      <c r="A65" s="9" t="inlineStr"/>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr"/>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>favor02_02</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>favor02</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>刚学打铁那会儿</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>好感度对话</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>铁匠</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>favor02_01</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>好感达到门槛</t>
         </is>
       </c>
-      <c r="I65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="11" t="n">
+      <c r="I65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M65" s="11" t="n">
+      <c r="M65" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N65" s="11" t="inlineStr">
+      <c r="N65" s="9" t="inlineStr">
         <is>
           <t>前段已读，与绑定NPC交谈且当前好感至少10时播放；开播前复核，读完不重复。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" s="3">
-      <c r="A66" s="9" t="inlineStr"/>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr"/>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>favor03_01</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>favor03</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>第一次上台</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>好感度对话</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>好感达到门槛</t>
         </is>
       </c>
-      <c r="I66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="11" t="n">
+      <c r="I66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="M66" s="11" t="n">
+      <c r="M66" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N66" s="11" t="inlineStr">
+      <c r="N66" s="9" t="inlineStr">
         <is>
           <t>NPC对玩家的当前好感至少5；首框显示时绑定本人，读完不重复。其他同职业NPC不共用这段往事。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" s="3">
-      <c r="A67" s="9" t="inlineStr"/>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr"/>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>favor03_02</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>favor03</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>第一次上台</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>好感度对话</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>吟游诗人</t>
         </is>
       </c>
-      <c r="G67" s="9" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>favor03_01</t>
         </is>
       </c>
-      <c r="H67" s="9" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>好感达到门槛</t>
         </is>
       </c>
-      <c r="I67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="11" t="n">
+      <c r="I67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M67" s="11" t="n">
+      <c r="M67" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="N67" s="11" t="inlineStr">
+      <c r="N67" s="9" t="inlineStr">
         <is>
           <t>前段已读，与绑定NPC交谈且当前好感至少10时播放；开播前复核，读完不重复。</t>
         </is>
